--- a/images/wcad.xlsx
+++ b/images/wcad.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\82104\OneDrive\바탕 화면\민간협회\국제파인아트디자인협회\세계어린이미술디자인대회\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\82104\OneDrive\바탕 화면\민간협회\국제파인아트디자인협회\1.세계어린이미술디자인대회\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
   <si>
     <t>번호</t>
   </si>
@@ -112,6 +112,10 @@
   </si>
   <si>
     <t>기관정보 ( ※ 필수 )</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>『 세계 어린이 미술&amp;디자인 대회 』 단체 참가작 명단</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -128,7 +132,7 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>기관명</t>
+      <t>기관명(학원명), 기관연락처, 학생명, 학년(유치부는 연령)</t>
     </r>
     <r>
       <rPr>
@@ -139,7 +143,7 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>’과 ‘</t>
+      <t>’ 동일하게 기재, 동명이인일 경우 ‘</t>
     </r>
     <r>
       <rPr>
@@ -151,7 +155,7 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>어린이 이름</t>
+      <t>작품제목</t>
     </r>
     <r>
       <rPr>
@@ -162,7 +166,7 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">’ 동일하게 기재, 동명이인일 경우 ‘작품제목’ 추가 기재 )
+      <t xml:space="preserve">’ 추가 기재 )
    - </t>
     </r>
     <r>
@@ -211,14 +215,6 @@
       </rPr>
       <t>이 인쇄됩니다.</t>
     </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>『 세계 어린이 미술&amp;디자인 대회 』 단체 참가작 명단</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>세라믹 조형</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -741,7 +737,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="43.15" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A1" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -754,7 +750,7 @@
     </row>
     <row r="2" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A2" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -862,7 +858,7 @@
       </c>
       <c r="O5" s="2"/>
     </row>
-    <row r="6" spans="1:15" ht="33" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:15" ht="19.149999999999999" x14ac:dyDescent="0.6">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -884,7 +880,7 @@
         <v>13</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>14</v>

--- a/images/wcad.xlsx
+++ b/images/wcad.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
   <si>
     <t>번호</t>
   </si>
@@ -39,9 +39,6 @@
   </si>
   <si>
     <t>대회부문</t>
-  </si>
-  <si>
-    <t>작품설명 ( ※ 있을 경우에만 작성 )</t>
   </si>
   <si>
     <t>김아트</t>
@@ -103,24 +100,24 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>우편번호</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>작품제목( ※ 필수 )</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>기관정보 ( ※ 필수 )</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>『 세계 어린이 미술&amp;디자인 대회 』 단체 참가작 명단</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>기관정보</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>작품설명 ( ※ 있을 경우에만 작성 )</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>제목(※필수/공백포함 25자 이내)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <r>
-      <t xml:space="preserve"> * 참가작 명단 ( 작품 뒷면에 ‘</t>
+      <t xml:space="preserve"> * 참가작 명단 ( </t>
     </r>
     <r>
       <rPr>
@@ -132,41 +129,39 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>기관명(학원명), 기관연락처, 학생명, 학년(유치부는 연령)</t>
+      <t>작품 뒷면 기재사항</t>
     </r>
     <r>
       <rPr>
-        <b/>
         <sz val="9"/>
         <rFont val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>’ 동일하게 기재, 동명이인일 경우 ‘</t>
+      <t xml:space="preserve">: </t>
     </r>
     <r>
       <rPr>
         <b/>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>작품제목</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
+        <u/>
         <sz val="9"/>
         <rFont val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">’ 추가 기재 )
+      <t>기관명(학원명), 기관연락처, 학생명, 학년(유치부는 연령)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">을 신청서와 동일하게 기재, 동명이인일 경우 ‘작품제목’ 추가 기재 )
    - </t>
     </r>
     <r>
@@ -183,7 +178,6 @@
     </r>
     <r>
       <rPr>
-        <b/>
         <sz val="9"/>
         <rFont val="맑은 고딕"/>
         <family val="3"/>
@@ -206,7 +200,6 @@
     </r>
     <r>
       <rPr>
-        <b/>
         <sz val="9"/>
         <rFont val="맑은 고딕"/>
         <family val="3"/>
@@ -222,7 +215,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -283,7 +276,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
+      <u/>
       <sz val="9"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
@@ -426,14 +427,14 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -715,7 +716,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O54"/>
+  <dimension ref="A1:N54"/>
   <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -726,18 +727,17 @@
     <col min="6" max="6" width="18.3125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.5625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.5" customWidth="1"/>
-    <col min="10" max="10" width="6.9375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.5625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.625" customWidth="1"/>
-    <col min="14" max="14" width="17.6875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="31.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.9375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.5625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.625" customWidth="1"/>
+    <col min="13" max="13" width="30.375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="31.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="43.15" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:14" ht="43.15" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A1" s="7" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -746,90 +746,88 @@
       <c r="F1" s="7"/>
       <c r="G1" s="7"/>
       <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-    </row>
-    <row r="2" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A2" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-    </row>
-    <row r="3" spans="1:15" ht="19.149999999999999" x14ac:dyDescent="0.6">
+    </row>
+    <row r="2" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A2" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+    </row>
+    <row r="3" spans="1:14" ht="19.149999999999999" x14ac:dyDescent="0.6">
       <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-    </row>
-    <row r="4" spans="1:15" ht="30.85" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="B3" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+    </row>
+    <row r="4" spans="1:14" ht="30.85" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A4" s="6"/>
       <c r="B4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>23</v>
+      <c r="I4" s="4" t="s">
+        <v>1</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="N4" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="O4" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="19.149999999999999" x14ac:dyDescent="0.6">
+    </row>
+    <row r="5" spans="1:14" ht="19.149999999999999" x14ac:dyDescent="0.6">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -840,7 +838,9 @@
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
+      <c r="I5" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="J5" s="1" t="s">
         <v>6</v>
       </c>
@@ -853,12 +853,9 @@
       <c r="M5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="N5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="O5" s="2"/>
-    </row>
-    <row r="6" spans="1:15" ht="19.149999999999999" x14ac:dyDescent="0.6">
+      <c r="N5" s="2"/>
+    </row>
+    <row r="6" spans="1:14" ht="19.149999999999999" x14ac:dyDescent="0.6">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -869,7 +866,9 @@
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
+      <c r="I6" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="J6" s="1" t="s">
         <v>11</v>
       </c>
@@ -877,17 +876,14 @@
         <v>12</v>
       </c>
       <c r="L6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="M6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="O6" s="2"/>
-    </row>
-    <row r="7" spans="1:15" ht="19.149999999999999" x14ac:dyDescent="0.6">
+      <c r="N6" s="2"/>
+    </row>
+    <row r="7" spans="1:14" ht="19.149999999999999" x14ac:dyDescent="0.6">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -898,15 +894,14 @@
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
+      <c r="I7" s="2"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
-    </row>
-    <row r="8" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.6">
+    </row>
+    <row r="8" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -917,15 +912,14 @@
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
+      <c r="I8" s="2"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-    </row>
-    <row r="9" spans="1:15" ht="19.149999999999999" x14ac:dyDescent="0.6">
+    </row>
+    <row r="9" spans="1:14" ht="19.149999999999999" x14ac:dyDescent="0.6">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -936,15 +930,14 @@
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
+      <c r="I9" s="2"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
-      <c r="O9" s="2"/>
-    </row>
-    <row r="10" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.6">
+    </row>
+    <row r="10" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A10" s="1">
         <v>6</v>
       </c>
@@ -955,15 +948,14 @@
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
+      <c r="I10" s="2"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
-    </row>
-    <row r="11" spans="1:15" ht="19.149999999999999" x14ac:dyDescent="0.6">
+    </row>
+    <row r="11" spans="1:14" ht="19.149999999999999" x14ac:dyDescent="0.6">
       <c r="A11" s="1">
         <v>7</v>
       </c>
@@ -974,15 +966,14 @@
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
+      <c r="I11" s="2"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-    </row>
-    <row r="12" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.6">
+    </row>
+    <row r="12" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A12" s="1">
         <v>8</v>
       </c>
@@ -993,15 +984,14 @@
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
+      <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
-    </row>
-    <row r="13" spans="1:15" ht="19.149999999999999" x14ac:dyDescent="0.6">
+    </row>
+    <row r="13" spans="1:14" ht="19.149999999999999" x14ac:dyDescent="0.6">
       <c r="A13" s="1">
         <v>9</v>
       </c>
@@ -1012,15 +1002,14 @@
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
+      <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
-    </row>
-    <row r="14" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.6">
+    </row>
+    <row r="14" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A14" s="1">
         <v>10</v>
       </c>
@@ -1031,15 +1020,14 @@
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
+      <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
-    </row>
-    <row r="15" spans="1:15" ht="19.149999999999999" x14ac:dyDescent="0.6">
+    </row>
+    <row r="15" spans="1:14" ht="19.149999999999999" x14ac:dyDescent="0.6">
       <c r="A15" s="1">
         <v>11</v>
       </c>
@@ -1050,15 +1038,14 @@
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
+      <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
-    </row>
-    <row r="16" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.6">
+    </row>
+    <row r="16" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A16" s="1">
         <v>12</v>
       </c>
@@ -1069,15 +1056,14 @@
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
+      <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
-    </row>
-    <row r="17" spans="1:15" ht="19.149999999999999" x14ac:dyDescent="0.6">
+    </row>
+    <row r="17" spans="1:14" ht="19.149999999999999" x14ac:dyDescent="0.6">
       <c r="A17" s="1">
         <v>13</v>
       </c>
@@ -1088,15 +1074,14 @@
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
+      <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
-    </row>
-    <row r="18" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.6">
+    </row>
+    <row r="18" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A18" s="1">
         <v>14</v>
       </c>
@@ -1107,15 +1092,14 @@
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
+      <c r="I18" s="2"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
-    </row>
-    <row r="19" spans="1:15" ht="19.149999999999999" x14ac:dyDescent="0.6">
+    </row>
+    <row r="19" spans="1:14" ht="19.149999999999999" x14ac:dyDescent="0.6">
       <c r="A19" s="1">
         <v>15</v>
       </c>
@@ -1126,15 +1110,14 @@
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
+      <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
       <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
-    </row>
-    <row r="20" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.6">
+    </row>
+    <row r="20" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A20" s="1">
         <v>16</v>
       </c>
@@ -1145,15 +1128,14 @@
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
+      <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
-    </row>
-    <row r="21" spans="1:15" ht="19.149999999999999" x14ac:dyDescent="0.6">
+    </row>
+    <row r="21" spans="1:14" ht="19.149999999999999" x14ac:dyDescent="0.6">
       <c r="A21" s="1">
         <v>17</v>
       </c>
@@ -1164,15 +1146,14 @@
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
+      <c r="I21" s="2"/>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
       <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
-    </row>
-    <row r="22" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.6">
+    </row>
+    <row r="22" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A22" s="1">
         <v>18</v>
       </c>
@@ -1183,15 +1164,14 @@
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
+      <c r="I22" s="2"/>
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
       <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
-    </row>
-    <row r="23" spans="1:15" ht="19.149999999999999" x14ac:dyDescent="0.6">
+    </row>
+    <row r="23" spans="1:14" ht="19.149999999999999" x14ac:dyDescent="0.6">
       <c r="A23" s="1">
         <v>19</v>
       </c>
@@ -1202,15 +1182,14 @@
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
+      <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
       <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
-    </row>
-    <row r="24" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.6">
+    </row>
+    <row r="24" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A24" s="1">
         <v>20</v>
       </c>
@@ -1221,15 +1200,14 @@
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
+      <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
-    </row>
-    <row r="25" spans="1:15" ht="19.149999999999999" x14ac:dyDescent="0.6">
+    </row>
+    <row r="25" spans="1:14" ht="19.149999999999999" x14ac:dyDescent="0.6">
       <c r="A25" s="1">
         <v>21</v>
       </c>
@@ -1240,15 +1218,14 @@
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
+      <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
       <c r="M25" s="2"/>
       <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
-    </row>
-    <row r="26" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.6">
+    </row>
+    <row r="26" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A26" s="1">
         <v>22</v>
       </c>
@@ -1259,15 +1236,14 @@
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
+      <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
-    </row>
-    <row r="27" spans="1:15" ht="19.149999999999999" x14ac:dyDescent="0.6">
+    </row>
+    <row r="27" spans="1:14" ht="19.149999999999999" x14ac:dyDescent="0.6">
       <c r="A27" s="1">
         <v>23</v>
       </c>
@@ -1278,15 +1254,14 @@
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
+      <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
-    </row>
-    <row r="28" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.6">
+    </row>
+    <row r="28" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A28" s="1">
         <v>24</v>
       </c>
@@ -1297,15 +1272,14 @@
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
+      <c r="I28" s="2"/>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
       <c r="M28" s="2"/>
       <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
-    </row>
-    <row r="29" spans="1:15" ht="19.149999999999999" x14ac:dyDescent="0.6">
+    </row>
+    <row r="29" spans="1:14" ht="19.149999999999999" x14ac:dyDescent="0.6">
       <c r="A29" s="1">
         <v>25</v>
       </c>
@@ -1316,15 +1290,14 @@
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
+      <c r="I29" s="2"/>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
       <c r="L29" s="2"/>
       <c r="M29" s="2"/>
       <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
-    </row>
-    <row r="30" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.6">
+    </row>
+    <row r="30" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A30" s="1">
         <v>26</v>
       </c>
@@ -1335,15 +1308,14 @@
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
+      <c r="I30" s="2"/>
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
       <c r="L30" s="2"/>
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
-    </row>
-    <row r="31" spans="1:15" ht="19.149999999999999" x14ac:dyDescent="0.6">
+    </row>
+    <row r="31" spans="1:14" ht="19.149999999999999" x14ac:dyDescent="0.6">
       <c r="A31" s="1">
         <v>27</v>
       </c>
@@ -1354,15 +1326,14 @@
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
+      <c r="I31" s="2"/>
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
       <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
-    </row>
-    <row r="32" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.6">
+    </row>
+    <row r="32" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A32" s="1">
         <v>28</v>
       </c>
@@ -1373,15 +1344,14 @@
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
+      <c r="I32" s="2"/>
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
       <c r="L32" s="2"/>
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
-    </row>
-    <row r="33" spans="1:15" ht="19.149999999999999" x14ac:dyDescent="0.6">
+    </row>
+    <row r="33" spans="1:14" ht="19.149999999999999" x14ac:dyDescent="0.6">
       <c r="A33" s="1">
         <v>29</v>
       </c>
@@ -1392,15 +1362,14 @@
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
+      <c r="I33" s="2"/>
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
       <c r="L33" s="2"/>
       <c r="M33" s="2"/>
       <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
-    </row>
-    <row r="34" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.6">
+    </row>
+    <row r="34" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A34" s="1">
         <v>30</v>
       </c>
@@ -1411,15 +1380,14 @@
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
+      <c r="I34" s="2"/>
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
       <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
-    </row>
-    <row r="35" spans="1:15" ht="19.149999999999999" x14ac:dyDescent="0.6">
+    </row>
+    <row r="35" spans="1:14" ht="19.149999999999999" x14ac:dyDescent="0.6">
       <c r="A35" s="1">
         <v>31</v>
       </c>
@@ -1430,15 +1398,14 @@
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
+      <c r="I35" s="2"/>
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
       <c r="L35" s="2"/>
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
-    </row>
-    <row r="36" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.6">
+    </row>
+    <row r="36" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A36" s="1">
         <v>32</v>
       </c>
@@ -1449,15 +1416,14 @@
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
+      <c r="I36" s="2"/>
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
       <c r="L36" s="2"/>
       <c r="M36" s="2"/>
       <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
-    </row>
-    <row r="37" spans="1:15" ht="19.149999999999999" x14ac:dyDescent="0.6">
+    </row>
+    <row r="37" spans="1:14" ht="19.149999999999999" x14ac:dyDescent="0.6">
       <c r="A37" s="1">
         <v>33</v>
       </c>
@@ -1468,15 +1434,14 @@
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
+      <c r="I37" s="2"/>
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
       <c r="L37" s="2"/>
       <c r="M37" s="2"/>
       <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
-    </row>
-    <row r="38" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.6">
+    </row>
+    <row r="38" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A38" s="1">
         <v>34</v>
       </c>
@@ -1487,15 +1452,14 @@
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
+      <c r="I38" s="2"/>
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
       <c r="L38" s="2"/>
       <c r="M38" s="2"/>
       <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
-    </row>
-    <row r="39" spans="1:15" ht="19.149999999999999" x14ac:dyDescent="0.6">
+    </row>
+    <row r="39" spans="1:14" ht="19.149999999999999" x14ac:dyDescent="0.6">
       <c r="A39" s="1">
         <v>35</v>
       </c>
@@ -1506,15 +1470,14 @@
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
+      <c r="I39" s="2"/>
       <c r="J39" s="2"/>
       <c r="K39" s="2"/>
       <c r="L39" s="2"/>
       <c r="M39" s="2"/>
       <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
-    </row>
-    <row r="40" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.6">
+    </row>
+    <row r="40" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A40" s="1">
         <v>36</v>
       </c>
@@ -1525,15 +1488,14 @@
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
+      <c r="I40" s="2"/>
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
       <c r="L40" s="2"/>
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
-    </row>
-    <row r="41" spans="1:15" ht="19.149999999999999" x14ac:dyDescent="0.6">
+    </row>
+    <row r="41" spans="1:14" ht="19.149999999999999" x14ac:dyDescent="0.6">
       <c r="A41" s="1">
         <v>37</v>
       </c>
@@ -1544,15 +1506,14 @@
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
+      <c r="I41" s="2"/>
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
       <c r="L41" s="2"/>
       <c r="M41" s="2"/>
       <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
-    </row>
-    <row r="42" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.6">
+    </row>
+    <row r="42" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A42" s="1">
         <v>38</v>
       </c>
@@ -1563,15 +1524,14 @@
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
+      <c r="I42" s="2"/>
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
       <c r="L42" s="2"/>
       <c r="M42" s="2"/>
       <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
-    </row>
-    <row r="43" spans="1:15" ht="19.149999999999999" x14ac:dyDescent="0.6">
+    </row>
+    <row r="43" spans="1:14" ht="19.149999999999999" x14ac:dyDescent="0.6">
       <c r="A43" s="1">
         <v>39</v>
       </c>
@@ -1582,15 +1542,14 @@
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
+      <c r="I43" s="2"/>
       <c r="J43" s="2"/>
       <c r="K43" s="2"/>
       <c r="L43" s="2"/>
       <c r="M43" s="2"/>
       <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
-    </row>
-    <row r="44" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.6">
+    </row>
+    <row r="44" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A44" s="1">
         <v>40</v>
       </c>
@@ -1601,15 +1560,14 @@
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
+      <c r="I44" s="2"/>
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
       <c r="L44" s="2"/>
       <c r="M44" s="2"/>
       <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
-    </row>
-    <row r="45" spans="1:15" ht="19.149999999999999" x14ac:dyDescent="0.6">
+    </row>
+    <row r="45" spans="1:14" ht="19.149999999999999" x14ac:dyDescent="0.6">
       <c r="A45" s="1">
         <v>41</v>
       </c>
@@ -1620,15 +1578,14 @@
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
-      <c r="I45" s="1"/>
+      <c r="I45" s="2"/>
       <c r="J45" s="2"/>
       <c r="K45" s="2"/>
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
       <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
-    </row>
-    <row r="46" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.6">
+    </row>
+    <row r="46" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A46" s="1">
         <v>42</v>
       </c>
@@ -1639,15 +1596,14 @@
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
+      <c r="I46" s="2"/>
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
       <c r="L46" s="2"/>
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
-    </row>
-    <row r="47" spans="1:15" ht="19.149999999999999" x14ac:dyDescent="0.6">
+    </row>
+    <row r="47" spans="1:14" ht="19.149999999999999" x14ac:dyDescent="0.6">
       <c r="A47" s="1">
         <v>43</v>
       </c>
@@ -1658,15 +1614,14 @@
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
       <c r="H47" s="1"/>
-      <c r="I47" s="1"/>
+      <c r="I47" s="2"/>
       <c r="J47" s="2"/>
       <c r="K47" s="2"/>
       <c r="L47" s="2"/>
       <c r="M47" s="2"/>
       <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
-    </row>
-    <row r="48" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.6">
+    </row>
+    <row r="48" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A48" s="1">
         <v>44</v>
       </c>
@@ -1677,15 +1632,14 @@
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
+      <c r="I48" s="2"/>
       <c r="J48" s="2"/>
       <c r="K48" s="2"/>
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
-    </row>
-    <row r="49" spans="1:15" ht="19.149999999999999" x14ac:dyDescent="0.6">
+    </row>
+    <row r="49" spans="1:14" ht="19.149999999999999" x14ac:dyDescent="0.6">
       <c r="A49" s="1">
         <v>45</v>
       </c>
@@ -1696,15 +1650,14 @@
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
       <c r="H49" s="1"/>
-      <c r="I49" s="1"/>
+      <c r="I49" s="2"/>
       <c r="J49" s="2"/>
       <c r="K49" s="2"/>
       <c r="L49" s="2"/>
       <c r="M49" s="2"/>
       <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
-    </row>
-    <row r="50" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.6">
+    </row>
+    <row r="50" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A50" s="1">
         <v>46</v>
       </c>
@@ -1715,15 +1668,14 @@
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
+      <c r="I50" s="2"/>
       <c r="J50" s="2"/>
       <c r="K50" s="2"/>
       <c r="L50" s="2"/>
       <c r="M50" s="2"/>
       <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
-    </row>
-    <row r="51" spans="1:15" ht="19.149999999999999" x14ac:dyDescent="0.6">
+    </row>
+    <row r="51" spans="1:14" ht="19.149999999999999" x14ac:dyDescent="0.6">
       <c r="A51" s="1">
         <v>47</v>
       </c>
@@ -1734,15 +1686,14 @@
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
+      <c r="I51" s="2"/>
       <c r="J51" s="2"/>
       <c r="K51" s="2"/>
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
       <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
-    </row>
-    <row r="52" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.6">
+    </row>
+    <row r="52" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A52" s="1">
         <v>48</v>
       </c>
@@ -1753,15 +1704,14 @@
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
-      <c r="I52" s="1"/>
+      <c r="I52" s="2"/>
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
       <c r="L52" s="2"/>
       <c r="M52" s="2"/>
       <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
-    </row>
-    <row r="53" spans="1:15" ht="19.149999999999999" x14ac:dyDescent="0.6">
+    </row>
+    <row r="53" spans="1:14" ht="19.149999999999999" x14ac:dyDescent="0.6">
       <c r="A53" s="1">
         <v>49</v>
       </c>
@@ -1772,15 +1722,14 @@
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
-      <c r="I53" s="1"/>
+      <c r="I53" s="2"/>
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
       <c r="L53" s="2"/>
       <c r="M53" s="2"/>
       <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
-    </row>
-    <row r="54" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.6">
+    </row>
+    <row r="54" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A54" s="1">
         <v>50</v>
       </c>
@@ -1791,24 +1740,23 @@
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
-      <c r="I54" s="1"/>
+      <c r="I54" s="2"/>
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
       <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="J3:O3"/>
-    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="I3:N3"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="A2:L2"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>